--- a/csv/model/DCC/formula_DCC_AT.xlsx
+++ b/csv/model/DCC/formula_DCC_AT.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="32175" yWindow="990" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -582,7 +582,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M131" t="n">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M132" t="n">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M133" t="n">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M134" t="n">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M135" t="n">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M136" t="n">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M137" t="n">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M138" t="n">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M139" t="n">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M140" t="n">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M141" t="n">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M142" t="n">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M143" t="n">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M144" t="n">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M145" t="n">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M146" t="n">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M147" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M148" t="n">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M149" t="n">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M150" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M151" t="n">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M152" t="n">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M153" t="n">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M154" t="n">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M155" t="n">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M156" t="n">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M157" t="n">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M158" t="n">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M159" t="n">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M160" t="n">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M161" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M162" t="n">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M163" t="n">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M164" t="n">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M165" t="n">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M166" t="n">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M167" t="n">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M168" t="n">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M169" t="n">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M170" t="n">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M171" t="n">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M172" t="n">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M173" t="n">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M174" t="n">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M175" t="n">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M176" t="n">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M177" t="n">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M178" t="n">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M179" t="n">
@@ -12854,7 +12854,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M180" t="n">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M181" t="n">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M182" t="n">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M183" t="n">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M184" t="n">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M185" t="n">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M186" t="n">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M187" t="n">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M188" t="n">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M189" t="n">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M190" t="n">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M191" t="n">
@@ -13694,7 +13694,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M192" t="n">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M193" t="n">
@@ -13834,7 +13834,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M194" t="n">
@@ -13904,7 +13904,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M195" t="n">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M196" t="n">
@@ -14044,7 +14044,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M197" t="n">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M198" t="n">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M199" t="n">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M200" t="n">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M201" t="n">
@@ -14394,7 +14394,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M202" t="n">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M203" t="n">
@@ -14534,7 +14534,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M204" t="n">
@@ -14604,7 +14604,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M205" t="n">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M206" t="n">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M207" t="n">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M208" t="n">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M209" t="n">
@@ -14954,7 +14954,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M210" t="n">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M211" t="n">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M212" t="n">
@@ -15164,7 +15164,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M213" t="n">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M214" t="n">
@@ -15304,7 +15304,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M215" t="n">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M216" t="n">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M217" t="n">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M218" t="n">
@@ -15584,7 +15584,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M219" t="n">
@@ -15654,7 +15654,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M220" t="n">
@@ -15724,7 +15724,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M221" t="n">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M222" t="n">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M223" t="n">
@@ -15934,7 +15934,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M224" t="n">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M225" t="n">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M226" t="n">
@@ -16144,7 +16144,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M227" t="n">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M228" t="n">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M229" t="n">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M230" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M231" t="n">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M232" t="n">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M233" t="n">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M234" t="n">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M235" t="n">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M236" t="n">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M237" t="n">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M238" t="n">
@@ -16984,7 +16984,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -17386,7 +17386,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -17433,7 +17433,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -17704,7 +17704,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -17836,7 +17836,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -17926,7 +17926,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18107,7 +18107,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -18324,7 +18324,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -18409,7 +18409,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -18500,7 +18500,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -18585,7 +18585,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -18627,7 +18627,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -18712,7 +18712,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -18797,7 +18797,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -18888,7 +18888,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -19020,7 +19020,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19110,7 +19110,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19200,7 +19200,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -19381,7 +19381,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -19423,7 +19423,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -19694,7 +19694,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -19784,7 +19784,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20006,7 +20006,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -20187,7 +20187,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -20319,7 +20319,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -20409,7 +20409,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -20590,7 +20590,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -20717,7 +20717,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -20807,7 +20807,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -20898,7 +20898,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -21115,7 +21115,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -21205,7 +21205,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -21296,7 +21296,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -21386,7 +21386,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -21428,7 +21428,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -21513,7 +21513,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -21603,7 +21603,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -21694,7 +21694,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -21826,7 +21826,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -21911,7 +21911,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22001,7 +22001,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -22092,7 +22092,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -22182,7 +22182,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -22224,7 +22224,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -22309,7 +22309,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -22399,7 +22399,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -22490,7 +22490,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -22580,7 +22580,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -22707,7 +22707,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -22968,7 +22968,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -23010,7 +23010,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -23095,7 +23095,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -23271,7 +23271,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -23398,7 +23398,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -23483,7 +23483,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -23568,7 +23568,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -23659,7 +23659,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -23786,7 +23786,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -23871,7 +23871,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -23956,7 +23956,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -24047,7 +24047,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -24132,7 +24132,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -24174,7 +24174,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -24259,7 +24259,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -24344,7 +24344,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -24435,7 +24435,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -24520,7 +24520,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -24562,7 +24562,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -24647,7 +24647,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -24732,7 +24732,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -24823,7 +24823,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -24908,7 +24908,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -24950,7 +24950,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -25035,7 +25035,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -25120,7 +25120,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -25211,7 +25211,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -25296,7 +25296,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -25338,7 +25338,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -25423,7 +25423,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -25508,7 +25508,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -25599,7 +25599,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -25684,7 +25684,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -25726,7 +25726,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -25896,7 +25896,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -25987,7 +25987,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -26114,7 +26114,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -26199,7 +26199,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -26284,7 +26284,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -26375,7 +26375,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -26460,7 +26460,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -26502,7 +26502,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -26587,7 +26587,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -26672,7 +26672,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -26763,7 +26763,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -26890,7 +26890,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -26975,7 +26975,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -27060,7 +27060,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -27236,7 +27236,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -27278,7 +27278,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -27363,7 +27363,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -27448,7 +27448,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -27539,7 +27539,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -27624,7 +27624,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -27666,7 +27666,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -27751,7 +27751,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -27836,7 +27836,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -27927,7 +27927,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
@@ -28012,7 +28012,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -28054,7 +28054,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -28315,7 +28315,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -28400,7 +28400,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -28442,7 +28442,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -28527,7 +28527,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -28703,7 +28703,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -28830,7 +28830,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -28915,7 +28915,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -29000,7 +29000,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
@@ -29091,7 +29091,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
@@ -29176,7 +29176,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -29218,7 +29218,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -29303,7 +29303,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
@@ -29388,7 +29388,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
@@ -29473,7 +29473,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
